--- a/histograms/histogram_Packing_fraction_avg.xlsx
+++ b/histograms/histogram_Packing_fraction_avg.xlsx
@@ -445,7 +445,7 @@
         <v>0.1277183953754235</v>
       </c>
       <c r="B2" t="n">
-        <v>160</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3">
@@ -469,7 +469,7 @@
         <v>0.2155630014321299</v>
       </c>
       <c r="B5" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -477,7 +477,7 @@
         <v>0.2448445367843654</v>
       </c>
       <c r="B6" t="n">
-        <v>1006</v>
+        <v>16</v>
       </c>
     </row>
     <row r="7">
@@ -485,7 +485,7 @@
         <v>0.2741260721366009</v>
       </c>
       <c r="B7" t="n">
-        <v>794</v>
+        <v>20</v>
       </c>
     </row>
     <row r="8">
@@ -493,7 +493,7 @@
         <v>0.3034076074888363</v>
       </c>
       <c r="B8" t="n">
-        <v>1013</v>
+        <v>15</v>
       </c>
     </row>
     <row r="9">
@@ -501,7 +501,7 @@
         <v>0.3326891428410719</v>
       </c>
       <c r="B9" t="n">
-        <v>3383</v>
+        <v>69</v>
       </c>
     </row>
     <row r="10">
@@ -509,7 +509,7 @@
         <v>0.3619706781933073</v>
       </c>
       <c r="B10" t="n">
-        <v>314</v>
+        <v>18</v>
       </c>
     </row>
     <row r="11">
@@ -517,7 +517,7 @@
         <v>0.3912522135455428</v>
       </c>
       <c r="B11" t="n">
-        <v>1806</v>
+        <v>28</v>
       </c>
     </row>
     <row r="12">
@@ -525,7 +525,7 @@
         <v>0.4205337488977783</v>
       </c>
       <c r="B12" t="n">
-        <v>5646</v>
+        <v>106</v>
       </c>
     </row>
     <row r="13">
@@ -533,7 +533,7 @@
         <v>0.4498152842500138</v>
       </c>
       <c r="B13" t="n">
-        <v>2208</v>
+        <v>72</v>
       </c>
     </row>
     <row r="14">
@@ -541,7 +541,7 @@
         <v>0.4790968196022493</v>
       </c>
       <c r="B14" t="n">
-        <v>1636</v>
+        <v>86</v>
       </c>
     </row>
     <row r="15">
@@ -549,7 +549,7 @@
         <v>0.5083783549544847</v>
       </c>
       <c r="B15" t="n">
-        <v>3519</v>
+        <v>77</v>
       </c>
     </row>
     <row r="16">
@@ -557,7 +557,7 @@
         <v>0.5376598903067202</v>
       </c>
       <c r="B16" t="n">
-        <v>3378</v>
+        <v>136</v>
       </c>
     </row>
     <row r="17">
@@ -565,7 +565,7 @@
         <v>0.5669414256589558</v>
       </c>
       <c r="B17" t="n">
-        <v>874</v>
+        <v>55</v>
       </c>
     </row>
     <row r="18">
@@ -573,7 +573,7 @@
         <v>0.5962229610111911</v>
       </c>
       <c r="B18" t="n">
-        <v>189</v>
+        <v>29</v>
       </c>
     </row>
     <row r="19">
@@ -581,7 +581,7 @@
         <v>0.6255044963634266</v>
       </c>
       <c r="B19" t="n">
-        <v>328</v>
+        <v>3</v>
       </c>
     </row>
     <row r="20">
@@ -589,7 +589,7 @@
         <v>0.6547860317156622</v>
       </c>
       <c r="B20" t="n">
-        <v>120</v>
+        <v>6</v>
       </c>
     </row>
     <row r="21">
@@ -597,7 +597,7 @@
         <v>0.6840675670678976</v>
       </c>
       <c r="B21" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
